--- a/Excel/ExclusiveSuitConfig.xlsx
+++ b/Excel/ExclusiveSuitConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="18">
   <si>
     <t>ID</t>
   </si>
@@ -36,6 +36,12 @@
   </si>
   <si>
     <t>Cycle</t>
+  </si>
+  <si>
+    <t>StartPart</t>
+  </si>
+  <si>
+    <t>EndPart</t>
   </si>
   <si>
     <t>AttrId</t>
@@ -1033,27 +1039,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
+  <dimension ref="A1:J32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="12.25" customWidth="1"/>
-    <col min="8" max="8" width="30.4833333333333" customWidth="1"/>
-    <col min="9" max="16368" width="9" style="2"/>
+    <col min="4" max="7" width="12.125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="12.25" customWidth="1"/>
+    <col min="10" max="10" width="30.4833333333333" customWidth="1"/>
+    <col min="11" max="16370" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="13" spans="1:2">
+    <row r="1" s="1" customFormat="1" spans="1:2">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="13" spans="1:2">
+    <row r="2" s="1" customFormat="1" spans="1:2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:8">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:10">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1074,12 +1080,18 @@
       <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="I3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:10">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
@@ -1096,106 +1108,142 @@
       <c r="H4" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="I4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:10">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="1" ht="27" customHeight="1" spans="3:8">
+    <row r="6" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>20</v>
+      </c>
+      <c r="H6">
         <v>301</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>1</v>
       </c>
-      <c r="H6" t="s">
-        <v>10</v>
+      <c r="J6" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="27" customHeight="1" spans="3:8">
+    <row r="7" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>54</v>
+        <v>1007</v>
       </c>
       <c r="G7">
+        <v>1012</v>
+      </c>
+      <c r="H7">
+        <v>55</v>
+      </c>
+      <c r="I7">
         <v>10</v>
       </c>
-      <c r="H7" t="s">
-        <v>12</v>
+      <c r="J7" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="8" customFormat="1" ht="27" customHeight="1" spans="3:8">
+    <row r="8" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8">
-        <v>55</v>
+        <v>1013</v>
       </c>
       <c r="G8">
+        <v>1018</v>
+      </c>
+      <c r="H8">
+        <v>54</v>
+      </c>
+      <c r="I8">
         <v>10</v>
       </c>
-      <c r="H8" t="s">
-        <v>14</v>
+      <c r="J8" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="9" customFormat="1" ht="27" customHeight="1" spans="3:8">
+    <row r="9" customFormat="1" ht="27" customHeight="1" spans="3:10">
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E9">
         <v>4</v>
       </c>
       <c r="F9">
+        <v>1019</v>
+      </c>
+      <c r="G9">
+        <v>1024</v>
+      </c>
+      <c r="H9">
         <v>-1</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>10</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>10</v>
       </c>
     </row>
@@ -1224,7 +1272,7 @@
     <row r="32" customFormat="1" ht="27" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D3 E3 C4:D4 E4 C5:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E3 F3 G3 C4:E4 F4 G4 C5:E5 F5 G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ExclusiveSuitConfig.xlsx
+++ b/Excel/ExclusiveSuitConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="19">
   <si>
     <t>ID</t>
   </si>
@@ -80,7 +80,10 @@
     <t>暴击增幅+10%</t>
   </si>
   <si>
-    <t>xx套装</t>
+    <t>粉色套装</t>
+  </si>
+  <si>
+    <t>神话全属性+10%</t>
   </si>
 </sst>
 </file>
@@ -1051,11 +1054,11 @@
     <col min="11" max="16370" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:2">
+    <row r="1" s="1" customFormat="1" ht="13" spans="1:10">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:2">
+    <row r="2" s="1" customFormat="1" ht="13" spans="1:10">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
     </row>
@@ -1143,7 +1146,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="1" ht="27" customHeight="1" spans="3:10">
+    <row r="6" customFormat="1" ht="27" customHeight="1" spans="1:10">
       <c r="C6">
         <v>1</v>
       </c>
@@ -1169,7 +1172,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="27" customHeight="1" spans="3:10">
+    <row r="7" customFormat="1" ht="27" customHeight="1" spans="1:10">
       <c r="C7">
         <v>2</v>
       </c>
@@ -1195,7 +1198,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" customFormat="1" ht="27" customHeight="1" spans="3:10">
+    <row r="8" customFormat="1" ht="27" customHeight="1" spans="1:10">
       <c r="C8">
         <v>3</v>
       </c>
@@ -1221,7 +1224,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" customFormat="1" ht="27" customHeight="1" spans="3:10">
+    <row r="9" customFormat="1" ht="27" customHeight="1" spans="1:10">
       <c r="C9">
         <v>4</v>
       </c>
@@ -1238,13 +1241,13 @@
         <v>1024</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>94</v>
       </c>
       <c r="I9">
         <v>10</v>
       </c>
-      <c r="J9">
-        <v>10</v>
+      <c r="J9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" customFormat="1" ht="27" customHeight="1"/>
@@ -1272,7 +1275,7 @@
     <row r="32" customFormat="1" ht="27" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E3 F3 G3 C4:E4 F4 G4 C5:E5 F5 G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
